--- a/forms/trg/Formulir_TRG_msm-rg.xlsx
+++ b/forms/trg/Formulir_TRG_msm-rg.xlsx
@@ -771,7 +771,7 @@
         </is>
       </c>
       <c r="B24" s="7">
-        <f>COUNTA(Anggota!B5:B25)</f>
+        <f>COUNTA(Anggota!B5:B26)</f>
         <v/>
       </c>
     </row>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!F5:F25)</f>
+        <f>COUNTA(Anggota!F5:F26)</f>
         <v/>
       </c>
     </row>
@@ -808,7 +808,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -913,22 +913,22 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Bualkar Abdullah, M.Eng.Sc.</t>
+          <t>Prof. Dr. Paulus Lobo Gareso, M.Sc.</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Leader</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Optoelectronics and Applied Electromagnetics</t>
+          <t>University of Hasanuddin</t>
         </is>
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Semiconductor Material</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
@@ -938,12 +938,12 @@
       <c r="J5" s="12" t="n"/>
       <c r="K5" s="11" t="inlineStr">
         <is>
-          <t>6018475</t>
+          <t>5979068</t>
         </is>
       </c>
       <c r="L5" s="11" t="inlineStr">
         <is>
-          <t>57193120779</t>
+          <t>6507410748</t>
         </is>
       </c>
       <c r="M5" s="11" t="inlineStr">
@@ -958,17 +958,17 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Nurlaela Rauf, M.Sc.</t>
+          <t>Prof. Dr. Bualkar Abdullah, M.Eng.Sc.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Ceramic Physics</t>
+          <t>Optoelectronics and Applied Electromagnetics</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
@@ -983,12 +983,12 @@
       <c r="J6" s="12" t="n"/>
       <c r="K6" s="11" t="inlineStr">
         <is>
-          <t>5981712</t>
+          <t>6018475</t>
         </is>
       </c>
       <c r="L6" s="11" t="inlineStr">
         <is>
-          <t>55387281600</t>
+          <t>57193120779</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Sri Suryani, DEA</t>
+          <t>Prof. Dr. Nurlaela Rauf, M.Sc.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>Biophysics</t>
+          <t>Ceramic Physics</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1028,12 +1028,12 @@
       <c r="J7" s="12" t="n"/>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6017401</t>
+          <t>5981712</t>
         </is>
       </c>
       <c r="L7" s="11" t="inlineStr">
         <is>
-          <t>6505957547</t>
+          <t>55387281600</t>
         </is>
       </c>
       <c r="M7" s="11" t="inlineStr">
@@ -1048,22 +1048,22 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. K. Veeravelan</t>
+          <t>Prof. Dr. Sri Suryani, DEA</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>‪Environmental Chemistry‬</t>
+          <t>Biophysics</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Department of Chemistry, Vel Tech Multi Tech Dr. Rangarajan Dr. Sakunthala Engineering College (Autonomous), Chennai, India</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1071,10 +1071,14 @@
       <c r="H8" s="12" t="n"/>
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
+      <c r="K8" s="11" t="inlineStr">
+        <is>
+          <t>6017401</t>
+        </is>
+      </c>
       <c r="L8" s="11" t="inlineStr">
         <is>
-          <t>60255987600</t>
+          <t>6505957547</t>
         </is>
       </c>
       <c r="M8" s="11" t="inlineStr">
@@ -1089,22 +1093,22 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Ahmed Akouibaa, Ph.D</t>
+          <t>Dr. K. Veeravelan</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>Optical Fiber-Based Biosensors</t>
+          <t>‪Environmental Chemistry‬</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
         <is>
-          <t>Sidi Mohamed Ben Abdellah University</t>
+          <t>Department of Chemistry, Vel Tech Multi Tech Dr. Rangarajan Dr. Sakunthala Engineering College (Autonomous), Chennai, India</t>
         </is>
       </c>
       <c r="F9" s="12" t="n"/>
@@ -1115,7 +1119,7 @@
       <c r="K9" s="12" t="n"/>
       <c r="L9" s="11" t="inlineStr">
         <is>
-          <t>58164787300</t>
+          <t>60255987600</t>
         </is>
       </c>
       <c r="M9" s="11" t="inlineStr">
@@ -1130,22 +1134,22 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Dr. Heryanto, S.Si., M.Si</t>
+          <t>Ahmed Akouibaa, Ph.D</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>Materials Computation</t>
+          <t>Optical Fiber-Based Biosensors</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
+          <t>Sidi Mohamed Ben Abdellah University</t>
         </is>
       </c>
       <c r="F10" s="12" t="n"/>
@@ -1153,14 +1157,10 @@
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6749103</t>
-        </is>
-      </c>
+      <c r="K10" s="12" t="n"/>
       <c r="L10" s="11" t="inlineStr">
         <is>
-          <t>57222594789</t>
+          <t>58164787300</t>
         </is>
       </c>
       <c r="M10" s="11" t="inlineStr">
@@ -1175,17 +1175,17 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Vicram Setiawan, S.Si.</t>
+          <t>Dr. Heryanto, S.Si., M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Researcher</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Material Electronics</t>
+          <t>Materials Computation</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -1198,10 +1198,14 @@
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6749103</t>
+        </is>
+      </c>
       <c r="L11" s="11" t="inlineStr">
         <is>
-          <t>59407316400</t>
+          <t>57222594789</t>
         </is>
       </c>
       <c r="M11" s="11" t="inlineStr">
@@ -1216,17 +1220,17 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Andi Akmal, S.Si</t>
+          <t>Vicram Setiawan, S.Si.</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>Electrocatalysis</t>
+          <t>Material Electronics</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -1242,7 +1246,7 @@
       <c r="K12" s="12" t="n"/>
       <c r="L12" s="11" t="inlineStr">
         <is>
-          <t>59241910600</t>
+          <t>59407316400</t>
         </is>
       </c>
       <c r="M12" s="11" t="inlineStr">
@@ -1257,17 +1261,17 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Nursalfaul Fahira, S.Si.</t>
+          <t>Andi Akmal, S.Si</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>Environmental Remediation</t>
+          <t>Electrocatalysis</t>
         </is>
       </c>
       <c r="E13" s="11" t="inlineStr">
@@ -1283,7 +1287,7 @@
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="11" t="inlineStr">
         <is>
-          <t>58650837100</t>
+          <t>59241910600</t>
         </is>
       </c>
       <c r="M13" s="11" t="inlineStr">
@@ -1296,18 +1300,42 @@
       <c r="A14" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Nursalfaul Fahira, S.Si.</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>The Multifunctional Semiconductor Materials group advances semiconductor science and engineering for sustainable tech. We design, synthesize, and characterize materials with tailored properties, integrating materials physics, nanotech, and green engineering to address global energy, environment, and smart tech challenges.</t>
+        </is>
+      </c>
       <c r="F14" s="12" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="n"/>
       <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
       <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-      <c r="M14" s="12" t="n"/>
+      <c r="L14" s="11" t="inlineStr">
+        <is>
+          <t>58650837100</t>
+        </is>
+      </c>
+      <c r="M14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -1496,15 +1524,32 @@
       <c r="L25" s="12" t="n"/>
       <c r="M25" s="12" t="n"/>
     </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
